--- a/public/test-data/03_2026_하반기_피어리뷰_최유진.xlsx
+++ b/public/test-data/03_2026_하반기_피어리뷰_최유진.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R4354336c4d004d2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_메타" sheetId="2" r:id="R67bd0e70578d4521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_신규 랜딩페이지 제작" sheetId="3" r:id="Rafc493d248fd434f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Cloud X 메인 UX 개선" sheetId="4" r:id="Rbd00fa7e43444431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_내부 협업툴 정비" sheetId="5" r:id="R99fd7081b1594a5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R1cd98190df0b4111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_메타" sheetId="2" r:id="Rc3ca284fc57f48a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_신규 랜딩페이지 제작" sheetId="3" r:id="Reb1cafe5ea7a43d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Cloud X 메인 UX 개선" sheetId="4" r:id="Rfd752c9a1839414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_내부 협업툴 정비" sheetId="5" r:id="R127c63860713432b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,62 +17,41 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="0"/>
-  </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="16"/>
+      <x:sz val="15"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:color rgb="FF111827"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FF667085"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10"/>
       <x:color rgb="FF111827"/>
-      <x:name val="Arial"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFF97316"/>
-      <x:name val="Arial"/>
+      <x:sz val="10"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="14"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF6B7280"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF059669"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FF16A34A"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -86,7 +65,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF9FAFB"/>
+        <x:fgColor rgb="FFF8FAFC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F4F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -96,11 +85,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFBEB"/>
+        <x:fgColor rgb="FFECFDF3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="5">
+  <x:borders count="2">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -116,47 +105,11 @@
         <x:color rgb="FFE5E7EB"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFFED7AA"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFFED7AA"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFFED7AA"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFFED7AA"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFFED7AA"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFFED7AA"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFFDE68A"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFFDE68A"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFFDE68A"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFFDE68A"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -166,57 +119,64 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -420,69 +380,57 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.110000133514404" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="71.11000061035156" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
+    <x:row r="1" ht="28.5" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>피어리뷰 입력 안내</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>평가기간</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>2026 하반기</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="8" t="str">
-        <x:v>평가자</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>최유진</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4"/>
-      <x:c r="B4"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>입력 방법</x:v>
-      </x:c>
-      <x:c r="B5" s="12"/>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="13" t="str">
+        <x:v>평가기간 2026 하반기 · 평가자 최유진</x:v>
+      </x:c>
+      <x:c r="B2" s="8"/>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="14" t="str">
+        <x:v>입력 안내</x:v>
+      </x:c>
+      <x:c r="B4" s="14"/>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="20" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>과제별 시트의 연한 입력 칸에 기여도와 수행등급을 입력합니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="13" t="str">
+      <x:c r="B5" s="20" t="str">
+        <x:v>과제별 시트에서 5명의 기여도·수행등급·근거를 확인하고 필요하면 수정합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="20" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>기여도 합계는 과제별로 100%가 되도록 확인합니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="13" t="str">
+      <x:c r="B6" s="20" t="str">
+        <x:v>각 과제의 기여도 합계는 100%여야 하며 합계 수식으로 자동 검증됩니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="20" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="14" t="str">
+      <x:c r="B7" s="20" t="str">
         <x:v>근거에는 관찰한 행동이나 결과를 짧고 구체적으로 작성합니다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="A4:B4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -492,39 +440,39 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24.440000534057617" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="19" t="str">
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="14" t="str">
         <x:v>구분</x:v>
       </x:c>
-      <x:c r="B1" s="19" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>값</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="13" t="str">
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" s="20" t="str">
         <x:v>평가기간</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="str">
+      <x:c r="B2" s="20" t="str">
         <x:v>2026 하반기</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="20" t="str">
         <x:v>평가자</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="20" t="str">
         <x:v>최유진</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="25" customHeight="1">
-      <x:c r="A4" s="13" t="str">
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="20" t="str">
         <x:v>양식버전</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="n">
+      <x:c r="B4" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -537,111 +485,125 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="51.11000061035156" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="21" t="str">
+    <x:row r="1" ht="28.5" customHeight="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>과제: 신규 랜딩페이지 제작</x:v>
       </x:c>
-      <x:c r="B1" s="21"/>
-      <x:c r="C1" s="21"/>
-      <x:c r="D1" s="21"/>
-    </x:row>
-    <x:row r="2" ht="23" customHeight="1">
-      <x:c r="A2" s="24" t="str">
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="21" t="str">
         <x:v>평가기간: 2026 하반기</x:v>
       </x:c>
-      <x:c r="B2" s="24"/>
-      <x:c r="C2" s="24"/>
-      <x:c r="D2" s="24"/>
-    </x:row>
-    <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="19" t="str">
+      <x:c r="B2" s="21"/>
+      <x:c r="C2" s="21"/>
+      <x:c r="D2" s="21"/>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="14" t="str">
         <x:v>평가 대상</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>기여도(%)</x:v>
       </x:c>
-      <x:c r="C3" s="19" t="str">
+      <x:c r="C3" s="14" t="str">
         <x:v>수행등급</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>근거</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="26" t="str">
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="20" t="str">
         <x:v>김민준</x:v>
       </x:c>
-      <x:c r="B4" s="25" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C4" s="25" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>프로젝트 목표와 일정 정리에 기여함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="26" t="str">
+      <x:c r="B4" s="28" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="str">
+        <x:v>S</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="str">
+        <x:v>신규 랜딩페이지 제작에서 맡은 산출물의 완성도와 협업 대응이 안정적이었습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="20" t="str">
         <x:v>이서연</x:v>
       </x:c>
-      <x:c r="B5" s="25" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C5" s="25" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>사용자 관점의 화면 개선을 수행함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="B5" s="28" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="str">
+        <x:v>신규 랜딩페이지 제작 진행 중 사용자 관점의 개선안을 구체적으로 제안했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="20" t="str">
         <x:v>박지훈</x:v>
       </x:c>
-      <x:c r="B6" s="25" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="25" t="str">
+      <x:c r="B6" s="28" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>안정적인 구현과 오류 대응을 지원함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="26" t="str">
+      <x:c r="D6" s="27" t="str">
+        <x:v>신규 랜딩페이지 제작에서 일정 공유와 의사결정 근거를 명확하게 정리했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="20" t="str">
         <x:v>최유진 (본인)</x:v>
       </x:c>
-      <x:c r="B7" s="25" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="25" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>콘텐츠 구성과 전환 데이터 분석을 주도함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="30" t="str">
+      <x:c r="B7" s="28" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D7" s="27" t="str">
+        <x:v>신규 랜딩페이지 제작의 주요 이슈를 빠르게 발견하고 해결 과정에 기여했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" s="20" t="str">
+        <x:v>정하늘</x:v>
+      </x:c>
+      <x:c r="B8" s="28" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="28" t="str">
+        <x:v>S</x:v>
+      </x:c>
+      <x:c r="D8" s="27" t="str">
+        <x:v>신규 랜딩페이지 제작에서 필요한 지원을 적시에 제공하고 후속 조치를 마무리했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" s="33" t="str">
         <x:v>기여도 합계</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="n">
-        <x:f>SUM(B4:B7)</x:f>
+      <x:c r="B9" s="33" t="n">
+        <x:f>SUM(B4:B8)</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="str">
+      <x:c r="C9" s="33" t="str">
         <x:v>검증</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="str">
-        <x:f>IF(B8=100,"정상","100% 확인")</x:f>
+      <x:c r="D9" s="33" t="str">
+        <x:f>IF(B9=100,"정상","100% 확인")</x:f>
         <x:v>정상</x:v>
       </x:c>
     </x:row>
@@ -651,11 +613,11 @@
     <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
   <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="B4:B7">
+    <x:dataValidation type="whole" operator="between" sqref="B4:B8">
       <x:formula1>0</x:formula1>
       <x:formula2>100</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C4:C7">
+    <x:dataValidation type="list" sqref="C4:C8">
       <x:formula1>"S,A,B,C,D"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -667,111 +629,125 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="51.11000061035156" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="21" t="str">
+    <x:row r="1" ht="28.5" customHeight="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>과제: Cloud X 메인 UX 개선</x:v>
       </x:c>
-      <x:c r="B1" s="21"/>
-      <x:c r="C1" s="21"/>
-      <x:c r="D1" s="21"/>
-    </x:row>
-    <x:row r="2" ht="23" customHeight="1">
-      <x:c r="A2" s="24" t="str">
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="21" t="str">
         <x:v>평가기간: 2026 하반기</x:v>
       </x:c>
-      <x:c r="B2" s="24"/>
-      <x:c r="C2" s="24"/>
-      <x:c r="D2" s="24"/>
-    </x:row>
-    <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="19" t="str">
+      <x:c r="B2" s="21"/>
+      <x:c r="C2" s="21"/>
+      <x:c r="D2" s="21"/>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="14" t="str">
         <x:v>평가 대상</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>기여도(%)</x:v>
       </x:c>
-      <x:c r="C3" s="19" t="str">
+      <x:c r="C3" s="14" t="str">
         <x:v>수행등급</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>근거</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="26" t="str">
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="20" t="str">
         <x:v>김민준</x:v>
       </x:c>
-      <x:c r="B4" s="25" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="25" t="str">
+      <x:c r="B4" s="28" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="str">
+        <x:v>Cloud X 메인 UX 개선에서 맡은 산출물의 완성도와 협업 대응이 안정적이었습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>이서연</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="str">
+        <x:v>Cloud X 메인 UX 개선 진행 중 사용자 관점의 개선안을 구체적으로 제안했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="20" t="str">
+        <x:v>박지훈</x:v>
+      </x:c>
+      <x:c r="B6" s="28" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>업무 우선순위와 의사결정을 지원함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>이서연</x:v>
-      </x:c>
-      <x:c r="B5" s="25" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C5" s="25" t="str">
+      <x:c r="D6" s="27" t="str">
+        <x:v>Cloud X 메인 UX 개선에서 일정 공유와 의사결정 근거를 명확하게 정리했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>최유진 (본인)</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>사용성 개선과 검증을 주도함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>박지훈</x:v>
-      </x:c>
-      <x:c r="B6" s="25" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C6" s="25" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>화면 구현과 성능 개선에 기여함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="26" t="str">
-        <x:v>최유진 (본인)</x:v>
-      </x:c>
-      <x:c r="B7" s="25" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C7" s="25" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>사용자 의견과 지표를 분석해 개선 근거를 제공함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="30" t="str">
+      <x:c r="D7" s="27" t="str">
+        <x:v>Cloud X 메인 UX 개선 진행 중 사용자 관점의 개선안을 구체적으로 제안했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" s="20" t="str">
+        <x:v>정하늘</x:v>
+      </x:c>
+      <x:c r="B8" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C8" s="28" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D8" s="27" t="str">
+        <x:v>Cloud X 메인 UX 개선 진행 중 사용자 관점의 개선안을 구체적으로 제안했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" s="33" t="str">
         <x:v>기여도 합계</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="n">
-        <x:f>SUM(B4:B7)</x:f>
+      <x:c r="B9" s="33" t="n">
+        <x:f>SUM(B4:B8)</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="str">
+      <x:c r="C9" s="33" t="str">
         <x:v>검증</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="str">
-        <x:f>IF(B8=100,"정상","100% 확인")</x:f>
+      <x:c r="D9" s="33" t="str">
+        <x:f>IF(B9=100,"정상","100% 확인")</x:f>
         <x:v>정상</x:v>
       </x:c>
     </x:row>
@@ -781,11 +757,11 @@
     <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
   <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="B4:B7">
+    <x:dataValidation type="whole" operator="between" sqref="B4:B8">
       <x:formula1>0</x:formula1>
       <x:formula2>100</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C4:C7">
+    <x:dataValidation type="list" sqref="C4:C8">
       <x:formula1>"S,A,B,C,D"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -797,111 +773,125 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="51.11000061035156" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="21" t="str">
+    <x:row r="1" ht="28.5" customHeight="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>과제: 내부 협업툴 정비</x:v>
       </x:c>
-      <x:c r="B1" s="21"/>
-      <x:c r="C1" s="21"/>
-      <x:c r="D1" s="21"/>
-    </x:row>
-    <x:row r="2" ht="23" customHeight="1">
-      <x:c r="A2" s="24" t="str">
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="21" t="str">
         <x:v>평가기간: 2026 하반기</x:v>
       </x:c>
-      <x:c r="B2" s="24"/>
-      <x:c r="C2" s="24"/>
-      <x:c r="D2" s="24"/>
-    </x:row>
-    <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="19" t="str">
+      <x:c r="B2" s="21"/>
+      <x:c r="C2" s="21"/>
+      <x:c r="D2" s="21"/>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="14" t="str">
         <x:v>평가 대상</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>기여도(%)</x:v>
       </x:c>
-      <x:c r="C3" s="19" t="str">
+      <x:c r="C3" s="14" t="str">
         <x:v>수행등급</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>근거</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="26" t="str">
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="20" t="str">
         <x:v>김민준</x:v>
       </x:c>
-      <x:c r="B4" s="25" t="n">
+      <x:c r="B4" s="28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="str">
+        <x:v>내부 협업툴 정비에서 필요한 지원을 적시에 제공하고 후속 조치를 마무리했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>이서연</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="str">
+        <x:v>내부 협업툴 정비에서 맡은 산출물의 완성도와 협업 대응이 안정적이었습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="20" t="str">
+        <x:v>박지훈</x:v>
+      </x:c>
+      <x:c r="B6" s="28" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="str">
+        <x:v>S</x:v>
+      </x:c>
+      <x:c r="D6" s="27" t="str">
+        <x:v>내부 협업툴 정비 진행 중 사용자 관점의 개선안을 구체적으로 제안했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>최유진 (본인)</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D7" s="27" t="str">
+        <x:v>내부 협업툴 정비에서 맡은 산출물의 완성도와 협업 대응이 안정적이었습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" s="20" t="str">
+        <x:v>정하늘</x:v>
+      </x:c>
+      <x:c r="B8" s="28" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C4" s="25" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>운영 프로세스 정리를 지원함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>이서연</x:v>
-      </x:c>
-      <x:c r="B5" s="25" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="25" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>화면 구조 개선 의견을 제공함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>박지훈</x:v>
-      </x:c>
-      <x:c r="B6" s="25" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C6" s="25" t="str">
+      <x:c r="C8" s="28" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>기능 안정화와 자동화에 기여함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="26" t="str">
-        <x:v>최유진 (본인)</x:v>
-      </x:c>
-      <x:c r="B7" s="25" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C7" s="25" t="str">
-        <x:v>S</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>운영 가이드와 데이터 체계를 정비함.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="30" t="str">
+      <x:c r="D8" s="27" t="str">
+        <x:v>내부 협업툴 정비에서 일정 공유와 의사결정 근거를 명확하게 정리했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" s="33" t="str">
         <x:v>기여도 합계</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="n">
-        <x:f>SUM(B4:B7)</x:f>
+      <x:c r="B9" s="33" t="n">
+        <x:f>SUM(B4:B8)</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="str">
+      <x:c r="C9" s="33" t="str">
         <x:v>검증</x:v>
       </x:c>
-      <x:c r="D8" s="32" t="str">
-        <x:f>IF(B8=100,"정상","100% 확인")</x:f>
+      <x:c r="D9" s="33" t="str">
+        <x:f>IF(B9=100,"정상","100% 확인")</x:f>
         <x:v>정상</x:v>
       </x:c>
     </x:row>
@@ -911,11 +901,11 @@
     <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
   <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="B4:B7">
+    <x:dataValidation type="whole" operator="between" sqref="B4:B8">
       <x:formula1>0</x:formula1>
       <x:formula2>100</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C4:C7">
+    <x:dataValidation type="list" sqref="C4:C8">
       <x:formula1>"S,A,B,C,D"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/public/test-data/03_2026_하반기_피어리뷰_최유진.xlsx
+++ b/public/test-data/03_2026_하반기_피어리뷰_최유진.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R1cd98190df0b4111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_메타" sheetId="2" r:id="Rc3ca284fc57f48a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_신규 랜딩페이지 제작" sheetId="3" r:id="Reb1cafe5ea7a43d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Cloud X 메인 UX 개선" sheetId="4" r:id="Rfd752c9a1839414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_내부 협업툴 정비" sheetId="5" r:id="R127c63860713432b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Rc690bcfb1d2f4d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_메타" sheetId="2" r:id="R06f8fd36c3b940fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_신규 랜딩페이지 제작" sheetId="3" r:id="R3b6556ce2d374700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Cloud X 메인 UX 개선" sheetId="4" r:id="R7afabc21125842e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_내부 협업툴 정비" sheetId="5" r:id="R6b9acd4140584dc4"/>
   </x:sheets>
 </x:workbook>
 </file>
